--- a/examples/jpetstore-6/.understand-anything/doc-output/si-단위테스트시나리오.xlsx
+++ b/examples/jpetstore-6/.understand-anything/doc-output/si-단위테스트시나리오.xlsx
@@ -187,12 +187,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>현황</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>기능 행의 진입점(라우트)·데이터(테이블×CRUD) 시드로 정상 흐름 1건 생성</t>
+          <t>확정 0/84 · 축소 생성 39/84 · 시험 수행결과 미연결 — 본 문서는 초안 스켈레톤(검토·보강 전제)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -205,12 +205,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>요구사항 인수조건(AC) 중 exception 유형당 1건(AC 문장 인용, 요구/AC 추적선 보존). 없으면 일반형 1건 + [미확인]</t>
+          <t>기능 행의 진입점(라우트)·데이터(테이블×CRUD) 시드로 정상 흐름 1건 생성</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -223,12 +223,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>예외</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>데이터 시드(0건·최대치) 기준 1건. 데이터 근거 없으면 일반형 + [미확인]</t>
+          <t>요구사항 인수조건(AC) 중 exception 유형당 1건(AC 문장 인용, 요구/AC 추적선 보존). 없으면 일반형 1건 + [미확인]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -241,12 +241,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>지위</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>전부 결정론 템플릿 생성 초안([추정]) — 대시보드 시험 탭에서 편집·확정하면 [확정] 승격(재생성에도 오버레이 유지)</t>
+          <t>데이터 시드(0건·최대치) 기준 1건. 데이터 근거 없으면 일반형 + [미확인]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -259,30 +259,48 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>지위</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>전부 결정론 템플릿 생성 초안([추정]) — 대시보드 시험 탭에서 편집·확정하면 [확정] 승격(재생성에도 오버레이 유지)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[추정]</t>
+        </is>
+      </c>
+      <c r="D6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>수행 기록</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>시나리오는 설계 초안 — 시험 수행 결과는 요구사항 AC 의 시험결과(TestRef)에 기록(확정 후 caseId 연결은 사람 몫)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>[추정]</t>
-        </is>
-      </c>
-      <c r="D6"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[추정]</t>
+        </is>
+      </c>
+      <c r="D7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D6"/>
+  <autoFilter ref="A1:D7"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="41" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -367,7 +385,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TS-FN-001-N1</t>
+          <t>TS-3653f930-N</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -426,7 +444,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TS-FN-001-E1</t>
+          <t>TS-3653f930-E</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +503,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TS-FN-001-B1</t>
+          <t>TS-3653f930-B</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -544,7 +562,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TS-FN-002-N1</t>
+          <t>TS-25737d9b-N</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -603,7 +621,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TS-FN-002-E1</t>
+          <t>TS-25737d9b-E</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -662,7 +680,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TS-FN-002-B1</t>
+          <t>TS-25737d9b-B</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -721,7 +739,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TS-FN-003-N1</t>
+          <t>TS-17db5e22-N</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -780,7 +798,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TS-FN-003-E1</t>
+          <t>TS-17db5e22-E</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -839,7 +857,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TS-FN-003-B1</t>
+          <t>TS-17db5e22-B</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -898,7 +916,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TS-FN-004-N1</t>
+          <t>TS-eb7ff746-N</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -957,7 +975,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TS-FN-004-E1</t>
+          <t>TS-eb7ff746-E</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1016,7 +1034,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TS-FN-004-B1</t>
+          <t>TS-eb7ff746-B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1075,7 +1093,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TS-FN-005-N1</t>
+          <t>TS-4c7a6412-N</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1134,7 +1152,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TS-FN-005-E1</t>
+          <t>TS-4c7a6412-E</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1193,7 +1211,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TS-FN-005-B1</t>
+          <t>TS-4c7a6412-B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1252,7 +1270,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TS-FN-006-N1</t>
+          <t>TS-04cfd5f5-N</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1311,7 +1329,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TS-FN-006-E1</t>
+          <t>TS-04cfd5f5-E</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1370,7 +1388,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TS-FN-006-B1</t>
+          <t>TS-04cfd5f5-B</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1429,7 +1447,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TS-FN-007-N1</t>
+          <t>TS-8f388341-N</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1488,7 +1506,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TS-FN-007-E1</t>
+          <t>TS-8f388341-E</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1547,7 +1565,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TS-FN-007-B1</t>
+          <t>TS-8f388341-B</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1606,7 +1624,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TS-FN-028-N1</t>
+          <t>TS-e64c2820-N</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1661,7 +1679,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TS-FN-028-E1</t>
+          <t>TS-e64c2820-E</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1716,7 +1734,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TS-FN-028-B1</t>
+          <t>TS-e64c2820-B</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1771,7 +1789,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TS-FN-026-N1</t>
+          <t>TS-df20f8e4-N</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1826,7 +1844,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TS-FN-026-E1</t>
+          <t>TS-df20f8e4-E</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1881,7 +1899,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TS-FN-026-B1</t>
+          <t>TS-df20f8e4-B</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1936,7 +1954,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TS-FN-027-N1</t>
+          <t>TS-c28dfd73-N</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1991,7 +2009,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TS-FN-027-E1</t>
+          <t>TS-c28dfd73-E:REQ-002:AC-4</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2054,7 +2072,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TS-FN-027-B1</t>
+          <t>TS-c28dfd73-B</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2109,7 +2127,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TS-FN-025-N1</t>
+          <t>TS-b853fe37-N</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2164,7 +2182,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TS-FN-025-E1</t>
+          <t>TS-b853fe37-E</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2219,7 +2237,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TS-FN-025-B1</t>
+          <t>TS-b853fe37-B</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2274,7 +2292,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TS-FN-023-N1</t>
+          <t>TS-6eced6a8-N</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2329,7 +2347,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TS-FN-023-E1</t>
+          <t>TS-6eced6a8-E</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2384,7 +2402,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TS-FN-023-B1</t>
+          <t>TS-6eced6a8-B</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2439,7 +2457,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TS-FN-024-N1</t>
+          <t>TS-f4c305f8-N</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2494,7 +2512,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TS-FN-024-E1</t>
+          <t>TS-f4c305f8-E:REQ-001:AC-4</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2557,7 +2575,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TS-FN-024-B1</t>
+          <t>TS-f4c305f8-B</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2612,7 +2630,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TS-FN-008-N1</t>
+          <t>TS-04f64890-N</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2671,7 +2689,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TS-FN-008-E1</t>
+          <t>TS-04f64890-E</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2730,7 +2748,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TS-FN-008-B1</t>
+          <t>TS-04f64890-B</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2789,7 +2807,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TS-FN-009-N1</t>
+          <t>TS-8b59c03c-N</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2848,7 +2866,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TS-FN-009-E1</t>
+          <t>TS-8b59c03c-E</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2907,7 +2925,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TS-FN-009-B1</t>
+          <t>TS-8b59c03c-B</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2966,7 +2984,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TS-FN-010-N1</t>
+          <t>TS-c92c4cb9-N</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3025,7 +3043,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TS-FN-010-E1</t>
+          <t>TS-c92c4cb9-E</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3084,7 +3102,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TS-FN-010-B1</t>
+          <t>TS-c92c4cb9-B</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3143,7 +3161,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TS-FN-011-N1</t>
+          <t>TS-51f32dbf-N</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3202,7 +3220,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TS-FN-011-E1</t>
+          <t>TS-51f32dbf-E</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3261,7 +3279,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TS-FN-011-B1</t>
+          <t>TS-51f32dbf-B</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3320,7 +3338,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TS-FN-012-N1</t>
+          <t>TS-0b6a73ab-N</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3379,7 +3397,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TS-FN-012-E1</t>
+          <t>TS-0b6a73ab-E</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3438,7 +3456,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TS-FN-012-B1</t>
+          <t>TS-0b6a73ab-B</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3497,7 +3515,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TS-FN-013-N1</t>
+          <t>TS-d65a8766-N</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3556,7 +3574,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TS-FN-013-E1</t>
+          <t>TS-d65a8766-E</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3615,7 +3633,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TS-FN-013-B1</t>
+          <t>TS-d65a8766-B</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3674,7 +3692,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TS-FN-014-N1</t>
+          <t>TS-3e8d32ff-N</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3733,7 +3751,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TS-FN-014-E1</t>
+          <t>TS-3e8d32ff-E</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3792,7 +3810,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TS-FN-014-B1</t>
+          <t>TS-3e8d32ff-B</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3851,7 +3869,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TS-FN-015-N1</t>
+          <t>TS-459d7e96-N</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3910,7 +3928,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TS-FN-015-E1</t>
+          <t>TS-459d7e96-E</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3969,7 +3987,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TS-FN-015-B1</t>
+          <t>TS-459d7e96-B</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4028,7 +4046,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TS-FN-016-N1</t>
+          <t>TS-477c47ac-N</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4087,7 +4105,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TS-FN-016-E1</t>
+          <t>TS-477c47ac-E</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4146,7 +4164,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TS-FN-016-B1</t>
+          <t>TS-477c47ac-B</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4205,7 +4223,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TS-FN-017-N1</t>
+          <t>TS-767ad04a-N</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4264,7 +4282,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TS-FN-017-E1</t>
+          <t>TS-767ad04a-E</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4323,7 +4341,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TS-FN-017-B1</t>
+          <t>TS-767ad04a-B</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4382,7 +4400,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TS-FN-018-N1</t>
+          <t>TS-613f4894-N</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4441,7 +4459,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TS-FN-018-E1</t>
+          <t>TS-613f4894-E</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4500,7 +4518,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TS-FN-018-B1</t>
+          <t>TS-613f4894-B</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4559,7 +4577,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TS-FN-019-N1</t>
+          <t>TS-8eddc158-N</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4618,7 +4636,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TS-FN-019-E1</t>
+          <t>TS-8eddc158-E</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4677,7 +4695,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TS-FN-019-B1</t>
+          <t>TS-8eddc158-B</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4736,7 +4754,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TS-FN-020-N1</t>
+          <t>TS-a885b63f-N</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4795,7 +4813,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TS-FN-020-E1</t>
+          <t>TS-a885b63f-E</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4854,7 +4872,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>TS-FN-020-B1</t>
+          <t>TS-a885b63f-B</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4913,7 +4931,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TS-FN-021-N1</t>
+          <t>TS-d7a0601e-N</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4972,7 +4990,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TS-FN-021-E1</t>
+          <t>TS-d7a0601e-E</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5031,7 +5049,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TS-FN-021-B1</t>
+          <t>TS-d7a0601e-B</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5090,7 +5108,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TS-FN-022-N1</t>
+          <t>TS-ef87ef36-N</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5149,7 +5167,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TS-FN-022-E1</t>
+          <t>TS-ef87ef36-E</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5208,7 +5226,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>TS-FN-022-B1</t>
+          <t>TS-ef87ef36-B</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">

--- a/examples/jpetstore-6/.understand-anything/doc-output/si-단위테스트시나리오.xlsx
+++ b/examples/jpetstore-6/.understand-anything/doc-output/si-단위테스트시나리오.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>정상 완료(오류 없음) + 데이터 반영 확인: ACCOUNT(CRU) · BANNERDATA(R) · PRODUCT(R) · PROFILE(CRU) · SIGNON(CRU)</t>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: ACCOUNT(RU) · BANNERDATA(R) · PRODUCT(R) · PROFILE(RU) · SIGNON(RU)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>경계 데이터 상태(대상 0건·최대치): ACCOUNT(CRU) · BANNERDATA(R) · PRODUCT(R) · PROFILE(CRU) · SIGNON(CRU)</t>
+          <t>경계 데이터 상태(대상 0건·최대치): ACCOUNT(RU) · BANNERDATA(R) · PRODUCT(R) · PROFILE(RU) · SIGNON(RU)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>정상 완료(오류 없음) + 데이터 반영 확인: ACCOUNT(CRU) · BANNERDATA(R) · PRODUCT(R) · PROFILE(CRU) · SIGNON(CRU)</t>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: ACCOUNT(CR) · BANNERDATA(R) · PRODUCT(R) · PROFILE(CR) · SIGNON(CR)</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>경계 데이터 상태(대상 0건·최대치): ACCOUNT(CRU) · BANNERDATA(R) · PRODUCT(R) · PROFILE(CRU) · SIGNON(CRU)</t>
+          <t>경계 데이터 상태(대상 0건·최대치): ACCOUNT(CR) · BANNERDATA(R) · PRODUCT(R) · PROFILE(CR) · SIGNON(CR)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>정상 완료(오류 없음) + 데이터 반영 확인: ACCOUNT(CRU) · BANNERDATA(R) · PRODUCT(R) · PROFILE(CRU) · SIGNON(CRU)</t>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: ACCOUNT(R) · BANNERDATA(R) · PRODUCT(R) · PROFILE(R) · SIGNON(R)</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>경계 데이터 상태(대상 0건·최대치): ACCOUNT(CRU) · BANNERDATA(R) · PRODUCT(R) · PROFILE(CRU) · SIGNON(CRU)</t>
+          <t>경계 데이터 상태(대상 0건·최대치): ACCOUNT(R) · BANNERDATA(R) · PRODUCT(R) · PROFILE(R) · SIGNON(R)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>정상 완료(오류 없음) + 데이터 반영 확인: INVENTORY(R) · ITEM(R)</t>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: ITEM(R)</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>경계 데이터 상태(대상 0건·최대치): INVENTORY(R) · ITEM(R)</t>
+          <t>경계 데이터 상태(대상 0건·최대치): ITEM(R)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>정상 완료(오류 없음) + 데이터 반영 확인: INVENTORY(R) · ITEM(R) · PRODUCT(R)</t>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: ITEM(R) · PRODUCT(R)</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>경계 데이터 상태(대상 0건·최대치): INVENTORY(R) · ITEM(R) · PRODUCT(R)</t>
+          <t>경계 데이터 상태(대상 0건·최대치): ITEM(R) · PRODUCT(R)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>정상 완료(오류 없음) + 데이터 반영 확인: ORDERS(CR) · ORDERSTATUS(CR)</t>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: ORDERS(R) · ORDERSTATUS(R)</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>경계 데이터 상태(대상 0건·최대치): ORDERS(CR) · ORDERSTATUS(CR)</t>
+          <t>경계 데이터 상태(대상 0건·최대치): ORDERS(R) · ORDERSTATUS(R)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>정상 완료(오류 없음) + 데이터 반영 확인: INVENTORY(RU) · ITEM(R) · LINEITEM(CR) · ORDERS(CR) · ORDERSTATUS(CR) · SEQUENCE(RU)</t>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: INVENTORY(U) · LINEITEM(C) · ORDERS(C) · ORDERSTATUS(C) · SEQUENCE(RU)</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>경계 데이터 상태(대상 0건·최대치): INVENTORY(RU) · ITEM(R) · LINEITEM(CR) · ORDERS(CR) · ORDERSTATUS(CR) · SEQUENCE(RU)</t>
+          <t>경계 데이터 상태(대상 0건·최대치): INVENTORY(U) · LINEITEM(C) · ORDERS(C) · ORDERSTATUS(C) · SEQUENCE(RU)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>정상 완료(오류 없음) + 데이터 반영 확인: INVENTORY(RU) · ITEM(R) · LINEITEM(CR) · ORDERS(CR) · ORDERSTATUS(CR)</t>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: INVENTORY(R) · ITEM(R) · LINEITEM(R) · ORDERS(R) · ORDERSTATUS(R)</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>경계 데이터 상태(대상 0건·최대치): INVENTORY(RU) · ITEM(R) · LINEITEM(CR) · ORDERS(CR) · ORDERSTATUS(CR)</t>
+          <t>경계 데이터 상태(대상 0건·최대치): INVENTORY(R) · ITEM(R) · LINEITEM(R) · ORDERS(R) · ORDERSTATUS(R)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">

--- a/examples/jpetstore-6/.understand-anything/doc-output/si-단위테스트시나리오.xlsx
+++ b/examples/jpetstore-6/.understand-anything/doc-output/si-단위테스트시나리오.xlsx
@@ -108,7 +108,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[미확인]</t>
+          <t>dfbb9822f7c17f41a39e96704f4ea4f455580278</t>
         </is>
       </c>
     </row>
